--- a/experiment_results/combined_sweep/rtt_bursts_S3_atk5pct_wu300000.xlsx
+++ b/experiment_results/combined_sweep/rtt_bursts_S3_atk5pct_wu300000.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -605,12 +605,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>108125</t>
+          <t>88654</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>174823</t>
+          <t>86216</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -719,12 +719,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>184294</t>
+          <t>98125</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>184611</t>
+          <t>86533</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>190455</t>
+          <t>103969</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>202194</t>
+          <t>98272</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -947,12 +947,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>185128</t>
+          <t>86903</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>180888</t>
+          <t>94032</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>182150</t>
+          <t>88165</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>166735</t>
+          <t>78617</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1175,12 +1175,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>157687</t>
+          <t>79117</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>155779</t>
+          <t>76710</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1289,12 +1289,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>140014</t>
+          <t>63351</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1346,12 +1346,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>103904</t>
+          <t>40600</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1403,12 +1403,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>51620</t>
+          <t>11067</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1460,12 +1460,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>21424</t>
+          <t>10403</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1517,12 +1517,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>20760</t>
+          <t>10403</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
